--- a/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37152</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65798</t>
+          <t>65648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59164</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86776</t>
+          <t>88411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112025</t>
+          <t>114605</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110784</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139775</t>
+          <t>140434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207958</t>
+          <t>207026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248186</t>
+          <t>245463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198292</t>
+          <t>195712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223541</t>
+          <t>221906</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213861</t>
+          <t>213202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242852</t>
+          <t>242681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415767</t>
+          <t>418490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455995</t>
+          <t>456927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49941</t>
+          <t>48734</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67899</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92562</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87846</t>
+          <t>87062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104881</t>
+          <t>105039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73601</t>
+          <t>74808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90916</t>
+          <t>91277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167561</t>
+          <t>168134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>148119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182265</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179082</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338020</t>
+          <t>337770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386435</t>
+          <t>388260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>321094</t>
+          <t>321252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353846</t>
+          <t>355240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315023</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>349085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645473</t>
+          <t>643648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693888</t>
+          <t>694138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61570</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35759</t>
+          <t>35515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>41777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56004</t>
+          <t>56012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74123</t>
+          <t>73890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>89751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117514</t>
+          <t>116689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107328</t>
+          <t>105452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135835</t>
+          <t>135058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205425</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243543</t>
+          <t>244450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187139</t>
+          <t>187964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214069</t>
+          <t>214902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203958</t>
+          <t>204735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232465</t>
+          <t>234341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>400903</t>
+          <t>399996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439021</t>
+          <t>440264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>68536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95222</t>
+          <t>93937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84931</t>
+          <t>85312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103305</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158503</t>
+          <t>159788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184108</t>
+          <t>185189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172586</t>
+          <t>172497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208284</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333641</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>384731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>330414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366195</t>
+          <t>366284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630525</t>
+          <t>631015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>682105</t>
+          <t>682492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45444</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26935</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>45940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61899</t>
+          <t>61734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>97696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126836</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>112110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143284</t>
+          <t>143692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219490</t>
+          <t>221835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262172</t>
+          <t>263595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221886</t>
+          <t>222166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249397</t>
+          <t>251026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236582</t>
+          <t>236174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266560</t>
+          <t>267756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>466416</t>
+          <t>464993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>509098</t>
+          <t>506753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>57561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78365</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105619</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>78466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97212</t>
+          <t>97650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87116</t>
+          <t>86987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104855</t>
+          <t>105459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>170338</t>
+          <t>171127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197592</t>
+          <t>196494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163082</t>
+          <t>162427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198848</t>
+          <t>199215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>169476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207870</t>
+          <t>207926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>346326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>393868</t>
+          <t>396908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>326175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362308</t>
+          <t>362963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363163</t>
+          <t>363107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397717</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702555</t>
+          <t>699515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754030</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>42029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48676</t>
+          <t>48502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86193</t>
+          <t>85659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13328</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>351501</t>
+          <t>352245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387146</t>
+          <t>389147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356940</t>
+          <t>361616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>411946</t>
+          <t>412997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>726689</t>
+          <t>721688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>789381</t>
+          <t>788355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73364</t>
+          <t>71363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109009</t>
+          <t>108265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104673</t>
+          <t>103622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>155003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187748</t>
+          <t>188774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250440</t>
+          <t>255441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>106569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123314</t>
+          <t>123238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130484</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152356</t>
+          <t>152619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243224</t>
+          <t>243794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270553</t>
+          <t>270055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>42982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52865</t>
+          <t>51782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62347</t>
+          <t>62845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89676</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>493743</t>
+          <t>493834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540208</t>
+          <t>542286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>543841</t>
+          <t>545068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>602518</t>
+          <t>601628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1056268</t>
+          <t>1051754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1130731</t>
+          <t>1125553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>122452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170995</t>
+          <t>170904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>160344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218131</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295979</t>
+          <t>301157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370442</t>
+          <t>374956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31941</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26175</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37165</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25830</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19762</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31930</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20238</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32122</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>45,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31941</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26058</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37609</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65648</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19430</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14206</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30632</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24532</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36700</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24340</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36224</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>54,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19430</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13762</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25313</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42185</t>
+          <t>40714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58448</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125043</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>111109</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>139210</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>100250</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88411</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>114605</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>87811</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>114550</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>125043</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>110955</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>140434</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>207026</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245463</t>
+          <t>245390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>228593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>214426</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>242527</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210067</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>195712</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>221906</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>195767</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>222506</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>67,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>228593</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>213202</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>242681</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418490</t>
+          <t>418563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456927</t>
+          <t>457725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40226</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32445</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48857</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39556</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31542</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49519</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31253</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48794</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40226</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32265</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48734</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>68885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91989</t>
+          <t>92052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83316</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74685</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91097</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>97025</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87062</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105039</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87787</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105328</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83316</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74808</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>91277</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>67,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168134</t>
+          <t>168071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192578</t>
+          <t>191238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>179147</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>213532</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>148119</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>182107</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>149198</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>182885</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>179464</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>214454</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337770</t>
+          <t>338740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388260</t>
+          <t>388537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>331338</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>315017</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>349402</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>337723</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>321252</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>355240</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>320474</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>354161</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>331338</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>314095</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>349085</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>643648</t>
+          <t>643371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694138</t>
+          <t>693168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26440</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19695</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32813</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25793</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19969</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19973</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32149</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26440</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20313</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33168</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>43817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61562</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35650</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29277</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>42395</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29691</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23200</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35515</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23335</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35511</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>35650</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28922</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41777</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73890</t>
+          <t>73757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>107766</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>136025</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>103602</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>89751</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>116689</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>91108</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>117163</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>121147</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>105452</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>135058</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244450</t>
+          <t>243303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>218646</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203768</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>232027</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>201051</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>187964</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>214902</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>187490</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>213545</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>218646</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>204735</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>234341</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399996</t>
+          <t>401143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>440264</t>
+          <t>439149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>41732</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33326</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51571</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>39675</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31515</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49213</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31727</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48746</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>41732</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32671</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51280</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68536</t>
+          <t>69750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93937</t>
+          <t>94030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95166</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85327</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103572</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77152</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67614</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68081</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85100</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>66,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>95166</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>85618</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104227</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159788</t>
+          <t>159695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185189</t>
+          <t>183975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>171369</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>208553</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>153097</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>186219</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>151473</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>186786</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>172497</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>208367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333254</t>
+          <t>332062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384731</t>
+          <t>381335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>349463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>330228</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>367412</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>446</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>307894</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>290746</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>323868</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>290179</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>325492</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>349463</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>330414</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>366284</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>631015</t>
+          <t>634411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>682492</t>
+          <t>683684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19094</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13693</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25112</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,01%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>18822</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13691</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24106</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13977</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24113</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19094</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24927</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32143</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26125</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37544</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>62,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21819</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16535</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26950</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16528</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26664</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32143</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26310</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37525</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45940</t>
+          <t>45630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61734</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>127957</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113034</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>142100</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>112739</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97696</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>126556</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>96898</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>125154</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>127957</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>112110</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>143692</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>221835</t>
+          <t>220860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263595</t>
+          <t>262103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251909</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>237766</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>266832</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>357</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>235983</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>222166</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>251026</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>223568</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>251824</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>67,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251909</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>236174</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>267756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,32%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464993</t>
+          <t>466485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506753</t>
+          <t>507728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43292</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34775</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52658</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47583</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38377</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57561</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38305</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56331</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43292</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34471</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52943</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79463</t>
+          <t>78296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>104206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96638</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>87272</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105155</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>88444</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78466</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97650</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79696</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97722</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>96638</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86987</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105459</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171127</t>
+          <t>171751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196494</t>
+          <t>197661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>172936</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>210538</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>162427</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>199215</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>161254</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>195993</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>169476</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>207926</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>346326</t>
+          <t>343486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396908</t>
+          <t>397367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>380690</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>360495</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>398097</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>346246</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>326175</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>362963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>329397</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>364136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>380690</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>363107</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>401557</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699515</t>
+          <t>699056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750097</t>
+          <t>752937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39041</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32029</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44451</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34366</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23088</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42029</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48502</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62502</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85659</t>
+          <t>77843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17691</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12281</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24703</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20312</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12649</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31590</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31023</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>42217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>368216</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>341303</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>385644</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>367721</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>352245</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>389147</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>391414</t>
+          <t>339453</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361616</t>
+          <t>324846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>412997</t>
+          <t>354373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>759135</t>
+          <t>707669</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>721688</t>
+          <t>681220</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>788355</t>
+          <t>729977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>107462</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90034</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>134375</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92789</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71363</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>108265</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>125205</t>
+          <t>92995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103622</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155003</t>
+          <t>107602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>217994</t>
+          <t>200457</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188774</t>
+          <t>178149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255441</t>
+          <t>226906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>131782</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>140815</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>72,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>115242</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106569</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123238</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>116327</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131567</t>
+          <t>107009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152619</t>
+          <t>124158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257825</t>
+          <t>248110</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243794</t>
+          <t>234422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270055</t>
+          <t>259699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27604</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46808</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>27,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34309</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26313</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42982</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40766</t>
+          <t>33649</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30730</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51782</t>
+          <t>42967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75075</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89106</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>512446</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>559254</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>730</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>517328</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>493834</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>542286</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>77,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487413</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>545068</t>
+          <t>469815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>601628</t>
+          <t>505058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1093778</t>
+          <t>1026453</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1051754</t>
+          <t>994310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1125553</t>
+          <t>1053621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>161789</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122452</t>
+          <t>141575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170904</t>
+          <t>188383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160344</t>
+          <t>124124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216904</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>332932</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301157</t>
+          <t>276390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>374956</t>
+          <t>335701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
